--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55263FD1-0B34-4BA0-83AD-225EA6B60010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168DFD3B-C66C-47E4-BDA6-2AD0F8AF4E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
